--- a/data/trans_dic/P1402-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1402-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,49</t>
+          <t>4,15; 7,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,08</t>
+          <t>4,9; 8,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,85</t>
+          <t>7,43; 11,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 12,35</t>
+          <t>8,28; 12,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,95</t>
+          <t>4,36; 8,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,42</t>
+          <t>5,44; 9,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,9</t>
+          <t>6,22; 10,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,33</t>
+          <t>4,68; 7,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,47</t>
+          <t>5,7; 8,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 10,6</t>
+          <t>7,4; 10,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,3</t>
+          <t>8,72; 11,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,31; 8,56</t>
+          <t>5,26; 8,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,23</t>
+          <t>5,14; 8,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,28</t>
+          <t>6,87; 10,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,44</t>
+          <t>7,37; 10,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,91</t>
+          <t>6,22; 9,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,95</t>
+          <t>6,45; 9,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,38</t>
+          <t>6,36; 10,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 9,32</t>
+          <t>6,74; 9,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,46</t>
+          <t>6,14; 8,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,44</t>
+          <t>6,23; 8,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 9,6</t>
+          <t>7,06; 9,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,82</t>
+          <t>7,53; 9,62</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,22</t>
+          <t>3,03; 6,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,77</t>
+          <t>5,43; 9,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 12,21</t>
+          <t>7,69; 12,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,24</t>
+          <t>7,15; 11,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,69</t>
+          <t>4,89; 8,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,69</t>
+          <t>6,58; 10,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 11,12</t>
+          <t>6,77; 11,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,93</t>
+          <t>5,21; 7,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,81</t>
+          <t>4,48; 6,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 9,53</t>
+          <t>6,57; 9,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,09</t>
+          <t>7,99; 11,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,08</t>
+          <t>6,55; 8,89</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,91</t>
+          <t>4,1; 6,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 11,33</t>
+          <t>7,45; 11,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,43</t>
+          <t>6,24; 9,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,44</t>
+          <t>8,01; 11,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,91</t>
+          <t>4,97; 8,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,3</t>
+          <t>8,6; 12,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 10,44</t>
+          <t>6,76; 10,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,08</t>
+          <t>6,33; 8,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,93</t>
+          <t>4,96; 7,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 11,18</t>
+          <t>8,6; 11,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 9,48</t>
+          <t>6,76; 9,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 9,2</t>
+          <t>7,51; 9,58</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,43</t>
+          <t>4,98; 6,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,43</t>
+          <t>6,61; 8,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 9,8</t>
+          <t>7,86; 9,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,84</t>
+          <t>8,37; 10,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,66</t>
+          <t>5,96; 7,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 9,62</t>
+          <t>7,71; 9,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,53</t>
+          <t>7,4; 9,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,75; 8,04</t>
+          <t>7,12; 8,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 6,85</t>
+          <t>5,68; 6,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,76</t>
+          <t>7,47; 8,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 9,31</t>
+          <t>7,91; 9,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,68</t>
+          <t>7,93; 9,05</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64185</t>
+          <t>69535</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66317</t>
+          <t>71119</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>130502</t>
+          <t>140654</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29411; 51992</t>
+          <t>28792; 53155</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36171; 63873</t>
+          <t>34475; 62033</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50161; 79958</t>
+          <t>50139; 80319</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52359; 78293</t>
+          <t>57057; 84696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30555; 54731</t>
+          <t>30038; 55988</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36422; 65653</t>
+          <t>37897; 65089</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42303; 73325</t>
+          <t>41869; 71102</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55997; 77280</t>
+          <t>60721; 83846</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65779; 101269</t>
+          <t>64725; 98243</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79627; 118661</t>
+          <t>79870; 118785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>101529; 142783</t>
+          <t>99678; 144051</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>114899; 147983</t>
+          <t>123996; 159415</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83301</t>
+          <t>92768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>76629</t>
+          <t>85291</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>159930</t>
+          <t>178060</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51111; 82306</t>
+          <t>50568; 84056</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52286; 83812</t>
+          <t>52365; 83966</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69609; 105115</t>
+          <t>70265; 105893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42150; 112521</t>
+          <t>77261; 111747</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60604; 95929</t>
+          <t>60231; 94673</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65631; 102375</t>
+          <t>66370; 102178</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69407; 108306</t>
+          <t>66279; 104940</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64478; 89195</t>
+          <t>72068; 99567</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120090; 163252</t>
+          <t>118574; 166384</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>125846; 172661</t>
+          <t>127547; 173345</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145386; 198189</t>
+          <t>145862; 198224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>99356; 189604</t>
+          <t>159466; 203597</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63283</t>
+          <t>71007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46307</t>
+          <t>51966</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109590</t>
+          <t>122973</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20623; 42171</t>
+          <t>20546; 43213</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41973; 74008</t>
+          <t>41135; 72460</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57647; 92710</t>
+          <t>58436; 92733</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50680; 79028</t>
+          <t>57291; 89055</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33750; 59426</t>
+          <t>33441; 58192</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51849; 83108</t>
+          <t>51102; 81738</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53170; 87315</t>
+          <t>53172; 88032</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22077; 64614</t>
+          <t>42313; 64642</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57933; 92718</t>
+          <t>61100; 94857</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100385; 146261</t>
+          <t>100778; 144974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121317; 171347</t>
+          <t>123477; 171500</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69541; 132160</t>
+          <t>105679; 143400</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89099</t>
+          <t>94850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>83437</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>163666</t>
+          <t>178287</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39599; 65066</t>
+          <t>38660; 64756</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69651; 107377</t>
+          <t>70606; 107521</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58190; 88395</t>
+          <t>58529; 89404</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73010; 105630</t>
+          <t>78986; 112314</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51493; 82153</t>
+          <t>51577; 83893</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>89406; 129409</t>
+          <t>90515; 131148</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70371; 109013</t>
+          <t>70544; 107979</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60015; 88146</t>
+          <t>70708; 97563</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97838; 137300</t>
+          <t>98226; 139156</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>168435; 223465</t>
+          <t>171888; 226019</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>136636; 187789</t>
+          <t>133964; 184421</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>141959; 185347</t>
+          <t>157945; 201515</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>299869</t>
+          <t>328160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>263819</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>563688</t>
+          <t>619974</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>161041; 210802</t>
+          <t>163060; 212361</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>226653; 288927</t>
+          <t>226560; 292023</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>268492; 332542</t>
+          <t>266855; 331080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>235490; 339621</t>
+          <t>295171; 360639</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>201167; 258756</t>
+          <t>201539; 255318</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>274080; 342156</t>
+          <t>273925; 343177</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>263158; 337702</t>
+          <t>262473; 336372</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>210216; 294073</t>
+          <t>265737; 316192</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>380100; 455760</t>
+          <t>377762; 457589</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>518037; 611320</t>
+          <t>521469; 609828</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>548885; 646291</t>
+          <t>548676; 639499</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>484867; 617312</t>
+          <t>575425; 656432</t>
         </is>
       </c>
     </row>
